--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488226_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488226_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1106</v>
+        <v>5.2304</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4689</v>
+        <v>4.0565</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6418</v>
+        <v>1.1739</v>
       </c>
       <c r="G2" t="n">
         <v>3.7374</v>
@@ -610,13 +610,13 @@
         <v>2.4087</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2054</v>
+        <v>0.3252</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8754</v>
+        <v>-0.2879</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0809</v>
+        <v>0.613</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3144</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7589</v>
+        <v>4.1718</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4807</v>
+        <v>1.7952</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2781</v>
+        <v>2.3766</v>
       </c>
       <c r="G3" t="n">
         <v>0.9281</v>
@@ -688,13 +688,13 @@
         <v>2.4087</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1627</v>
+        <v>-0.4244</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9737</v>
+        <v>0.2882</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8111</v>
+        <v>-0.7126</v>
       </c>
       <c r="V3" t="n">
         <v>1.2594</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4572</v>
+        <v>3.6542</v>
       </c>
       <c r="E4" t="n">
         <v>3.0634</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3938</v>
+        <v>0.5908</v>
       </c>
       <c r="G4" t="n">
         <v>2.4901</v>
@@ -766,13 +766,13 @@
         <v>2.0382</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.774</v>
+        <v>-0.577</v>
       </c>
       <c r="T4" t="n">
         <v>-0.2773</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4967</v>
+        <v>-0.2997</v>
       </c>
       <c r="V4" t="n">
         <v>0.6294</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>J. WOJCIK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9846</v>
+        <v>1.9918</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0856</v>
+        <v>1.4578</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.1011</v>
+        <v>0.534</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.3612</v>
+        <v>1.5056</v>
       </c>
       <c r="H5" t="n">
-        <v>0.766</v>
+        <v>2.048</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.1272</v>
+        <v>-0.5424</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1478</v>
+        <v>2.6615</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0648</v>
+        <v>1.9754</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0829</v>
+        <v>0.6861</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.509</v>
+        <v>-1.156</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2989</v>
+        <v>0.0726</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.2101</v>
+        <v>-1.2285</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9264</v>
+        <v>2.0382</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5136</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0321</v>
+        <v>-0.2773</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4815</v>
+        <v>-0.3482</v>
       </c>
       <c r="V5" t="n">
-        <v>2.8321</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.8321</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. WOJCIK</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7456</v>
+        <v>1.2006</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4578</v>
+        <v>3.4001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2878</v>
+        <v>-2.1995</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5056</v>
+        <v>-2.3612</v>
       </c>
       <c r="H6" t="n">
-        <v>2.048</v>
+        <v>0.766</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5424</v>
+        <v>-3.1272</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6615</v>
+        <v>1.1478</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9754</v>
+        <v>1.0648</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6861</v>
+        <v>0.0829</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.156</v>
+        <v>-3.509</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0726</v>
+        <v>-0.2989</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2285</v>
+        <v>-3.2101</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0382</v>
+        <v>0.9264</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8717</v>
+        <v>0.7296</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2773</v>
+        <v>0.3466</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5944</v>
+        <v>0.383</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.8321</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.8321</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. ALOGO EVUNA</t>
+          <t>A. MENDEZ CARRION</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3423</v>
+        <v>0.453</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1227</v>
+        <v>-1.5121</v>
       </c>
       <c r="F7" t="n">
-        <v>0.465</v>
+        <v>1.965</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3261</v>
+        <v>4.6079</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5687</v>
+        <v>2.4083</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2427</v>
+        <v>2.1996</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0415</v>
+        <v>4.3891</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.3357</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0415</v>
+        <v>2.0535</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2846</v>
+        <v>0.2188</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5687</v>
+        <v>0.0726</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2841</v>
+        <v>0.1462</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-3.1499</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-5.5586</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.4087</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2987</v>
+        <v>-0.3762</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1641</v>
+        <v>-0.3426</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1346</v>
+        <v>-0.0336</v>
       </c>
       <c r="V7" t="n">
-        <v>0.315</v>
+        <v>-0.6289</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.315</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MENDEZ CARRION</t>
+          <t>R. ALOGO EVUNA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.3177</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0996</v>
+        <v>-0.1227</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1866</v>
+        <v>0.4404</v>
       </c>
       <c r="G9" t="n">
-        <v>4.6079</v>
+        <v>0.3261</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4083</v>
+        <v>0.5687</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1996</v>
+        <v>-0.2427</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3891</v>
+        <v>0.0415</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3357</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2.0535</v>
+        <v>0.0415</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2188</v>
+        <v>0.2846</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0726</v>
+        <v>0.5687</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1462</v>
+        <v>-0.2841</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.1499</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.5586</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4087</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7422</v>
+        <v>-0.3233</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9302</v>
+        <v>-0.1641</v>
       </c>
       <c r="U9" t="n">
-        <v>0.188</v>
+        <v>-0.1592</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6289</v>
+        <v>0.315</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6289</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTIN</t>
+          <t>A. MEJIA BERIGUETE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2438</v>
+        <v>-0.4735</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0477</v>
+        <v>0.6017</v>
       </c>
       <c r="F10" t="n">
-        <v>0.804</v>
+        <v>-1.0752</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8247</v>
+        <v>-0.9905</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.585</v>
+        <v>-0.0552</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2398</v>
+        <v>-0.9354</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2629</v>
+        <v>1.1056</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6314</v>
+        <v>-0.2322</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6315</v>
+        <v>1.3378</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4381</v>
+        <v>-2.0961</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0464</v>
+        <v>0.177</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3917</v>
+        <v>-2.2731</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1853</v>
+        <v>0.3706</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7411</v>
+        <v>1.297</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7663</v>
+        <v>0.1464</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1416</v>
+        <v>0.4225</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3753</v>
+        <v>-0.2761</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MEJIA BERIGUETE</t>
+          <t>J. NIELSEN HIDALGO MARTIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7192</v>
+        <v>-0.7088</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5037</v>
+        <v>-1.5374</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2229</v>
+        <v>0.8286</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9905</v>
+        <v>-0.8247</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0552</v>
+        <v>-0.585</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9354</v>
+        <v>-0.2398</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1056</v>
+        <v>-1.2629</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2322</v>
+        <v>-0.6314</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3378</v>
+        <v>-0.6315</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0961</v>
+        <v>0.4381</v>
       </c>
       <c r="N11" t="n">
-        <v>0.177</v>
+        <v>0.0464</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.2731</v>
+        <v>0.3917</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3706</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R11" t="n">
-        <v>1.297</v>
+        <v>0.7411</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0992</v>
+        <v>0.3013</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3246</v>
+        <v>0.6519</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4238</v>
+        <v>-0.3507</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6733</v>
+        <v>-1.7466</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5628</v>
+        <v>-1.6608</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1104</v>
+        <v>-0.0858</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0258</v>
@@ -1390,13 +1390,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0376</v>
+        <v>-0.0358</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5434</v>
+        <v>0.4455</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5059</v>
+        <v>-0.4813</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3144</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.533</v>
+        <v>-1.7982</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7822</v>
+        <v>1.4677</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.3152</v>
+        <v>-3.2659</v>
       </c>
       <c r="G13" t="n">
         <v>-3.1199</v>
@@ -1468,13 +1468,13 @@
         <v>1.6676</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7842</v>
+        <v>-0.0494</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4377</v>
+        <v>0.2478</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3465</v>
+        <v>-0.2972</v>
       </c>
       <c r="V13" t="n">
         <v>0.63</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.578</v>
+        <v>-2.5534</v>
       </c>
       <c r="E14" t="n">
         <v>-0.7526</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8254</v>
+        <v>-1.8008</v>
       </c>
       <c r="G14" t="n">
         <v>-2.6156</v>
@@ -1546,13 +1546,13 @@
         <v>0.1853</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1477</v>
+        <v>-0.1231</v>
       </c>
       <c r="T14" t="n">
         <v>-0.1641</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,16 +1579,16 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.061</v>
+        <v>10.0611</v>
       </c>
       <c r="E15" t="n">
-        <v>10.579</v>
+        <v>10.5789</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5179000000000007</v>
+        <v>-0.5178999999999998</v>
       </c>
       <c r="G15" t="n">
-        <v>2.979599999999998</v>
+        <v>2.9796</v>
       </c>
       <c r="H15" t="n">
         <v>13.3471</v>
@@ -1609,7 +1609,7 @@
         <v>-13.0718</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4785</v>
+        <v>-0.4785000000000001</v>
       </c>
       <c r="O15" t="n">
         <v>-12.5933</v>
@@ -1624,13 +1624,13 @@
         <v>16.6758</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0321</v>
+        <v>-1.0322</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8893000000000001</v>
+        <v>0.8891999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.9215</v>
+        <v>-1.9216</v>
       </c>
       <c r="V15" t="n">
         <v>4.4082</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MIAVIVULULU NZIKULU</t>
+          <t>J. RIBEIROS CARREIRAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.149</v>
+        <v>1.7167</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6818</v>
+        <v>3.8161</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-2.0993</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0703</v>
+        <v>4.3265</v>
       </c>
       <c r="H16" t="n">
-        <v>-5.1897</v>
+        <v>-2.049</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1194</v>
+        <v>6.3755</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8898</v>
+        <v>7.4066</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.3676</v>
+        <v>0.8931</v>
       </c>
       <c r="L16" t="n">
-        <v>5.2574</v>
+        <v>6.5135</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9601</v>
+        <v>-3.0801</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8221</v>
+        <v>-2.9421</v>
       </c>
       <c r="O16" t="n">
         <v>-0.138</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.6676</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.7057</v>
+        <v>-2.7793</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0382</v>
+        <v>2.2234</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5725</v>
+        <v>-0.1651</v>
       </c>
       <c r="T16" t="n">
-        <v>4.1833</v>
+        <v>-0.1812</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6108</v>
+        <v>0.0161</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3144</v>
+        <v>-1.8888</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3144</v>
+        <v>-0.63</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="17">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4999</v>
+        <v>0.5245</v>
       </c>
       <c r="E18" t="n">
         <v>0.5409</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.041</v>
+        <v>-0.0164</v>
       </c>
       <c r="G18" t="n">
         <v>0.5367</v>
@@ -1858,13 +1858,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2783</v>
+        <v>-0.2537</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1641</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1142</v>
+        <v>-0.0895</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3144</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. RIBEIROS CARREIRAS</t>
+          <t>J. RICARDO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2455</v>
+        <v>0.3699</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7388</v>
+        <v>0.9284</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4933</v>
+        <v>-0.5584</v>
       </c>
       <c r="G19" t="n">
-        <v>4.3265</v>
+        <v>1.1096</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.049</v>
+        <v>1.2923</v>
       </c>
       <c r="I19" t="n">
-        <v>6.3755</v>
+        <v>-0.1827</v>
       </c>
       <c r="J19" t="n">
-        <v>7.4066</v>
+        <v>3.6527</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8931</v>
+        <v>3.4133</v>
       </c>
       <c r="L19" t="n">
-        <v>6.5135</v>
+        <v>0.2394</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.0801</v>
+        <v>-2.5431</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.9421</v>
+        <v>-2.121</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.138</v>
+        <v>-0.4221</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.7793</v>
+        <v>-3.7057</v>
       </c>
       <c r="R19" t="n">
         <v>2.2234</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6362</v>
+        <v>0.1138</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2584</v>
+        <v>0.3526</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3778</v>
+        <v>-0.2388</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8888</v>
+        <v>0.6289</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.63</v>
+        <v>0.6289</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. RICARDO</t>
+          <t>M. MOLINA LOPEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0264</v>
+        <v>-0.164</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7325</v>
+        <v>-0.8452</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7062</v>
+        <v>0.6813</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1096</v>
+        <v>-1.2884</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2923</v>
+        <v>-0.8676</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1827</v>
+        <v>-0.4209</v>
       </c>
       <c r="J20" t="n">
-        <v>3.6527</v>
+        <v>-1.1813</v>
       </c>
       <c r="K20" t="n">
-        <v>3.4133</v>
+        <v>-0.6529</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2394</v>
+        <v>-0.5284</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.5431</v>
+        <v>-0.1071</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.121</v>
+        <v>-0.2147</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4221</v>
+        <v>0.1076</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.4823</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2234</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2298</v>
+        <v>0.5686</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1567</v>
+        <v>0.3361</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3865</v>
+        <v>0.2325</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MOLINA LOPEZ</t>
+          <t>J. MIAVIVULULU NZIKULU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0414</v>
+        <v>-0.2735</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7473</v>
+        <v>0.0377</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7059</v>
+        <v>-0.3112</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2884</v>
+        <v>-0.0703</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8676</v>
+        <v>-5.1897</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4209</v>
+        <v>5.1194</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1813</v>
+        <v>1.8898</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6529</v>
+        <v>-3.3676</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5284</v>
+        <v>5.2574</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1071</v>
+        <v>-1.9601</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2147</v>
+        <v>-1.8221</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1076</v>
+        <v>-0.138</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5558999999999999</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5558999999999999</v>
+        <v>2.0382</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6912</v>
+        <v>1.15</v>
       </c>
       <c r="T21" t="n">
-        <v>0.434</v>
+        <v>1.5392</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2572</v>
+        <v>-0.3892</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1529</v>
+        <v>-1.2022</v>
       </c>
       <c r="E22" t="n">
         <v>0.0017</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1547</v>
+        <v>-1.2039</v>
       </c>
       <c r="G22" t="n">
         <v>0.2358</v>
@@ -2170,13 +2170,13 @@
         <v>0.1853</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3151</v>
+        <v>-0.3644</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1641</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.151</v>
+        <v>-0.2002</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2589</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6875</v>
+        <v>-1.246</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2793</v>
+        <v>-0.9855</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4082</v>
+        <v>-0.2605</v>
       </c>
       <c r="G23" t="n">
         <v>-1.786</v>
@@ -2248,13 +2248,13 @@
         <v>1.1117</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0132</v>
+        <v>-0.5717</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3283</v>
+        <v>-0.0345</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6849</v>
+        <v>-0.5372</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0979</v>
+        <v>-1.8774</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0494</v>
+        <v>0.2452</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1473</v>
+        <v>-2.1227</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2982</v>
@@ -2326,13 +2326,13 @@
         <v>0.3706</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4847</v>
+        <v>-0.2643</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.383</v>
+        <v>-0.1871</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1017</v>
+        <v>-0.0771</v>
       </c>
       <c r="V24" t="n">
         <v>0.3144</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.3884</v>
+        <v>-2.9738</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.7099</v>
+        <v>-0.0244</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.6785</v>
+        <v>-2.9493</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6363</v>
@@ -2404,13 +2404,13 @@
         <v>1.297</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4927</v>
+        <v>-0.078</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.766</v>
+        <v>-0.0805</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2733</v>
+        <v>0.0025</v>
       </c>
       <c r="V25" t="n">
         <v>-0.63</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.2357</v>
+        <v>-5.5574</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.1127</v>
+        <v>-3.8189</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.123</v>
+        <v>-1.7385</v>
       </c>
       <c r="G26" t="n">
         <v>-1.7306</v>
@@ -2482,13 +2482,13 @@
         <v>2.4087</v>
       </c>
       <c r="S26" t="n">
-        <v>1.2187</v>
+        <v>0.8969</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2114</v>
+        <v>0.5052</v>
       </c>
       <c r="U26" t="n">
-        <v>1.0072</v>
+        <v>0.3917</v>
       </c>
       <c r="V26" t="n">
         <v>-1.5738</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-10.0609</v>
+        <v>-10.0611</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5180000000000007</v>
+        <v>0.5181000000000004</v>
       </c>
       <c r="F27" t="n">
-        <v>-10.5791</v>
+        <v>-10.5789</v>
       </c>
       <c r="G27" t="n">
         <v>-2.9791</v>
@@ -2560,10 +2560,10 @@
         <v>12.9701</v>
       </c>
       <c r="S27" t="n">
-        <v>1.0324</v>
+        <v>1.0321</v>
       </c>
       <c r="T27" t="n">
-        <v>1.9215</v>
+        <v>1.9216</v>
       </c>
       <c r="U27" t="n">
         <v>-0.8892000000000002</v>
